--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488124_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488124_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.259</v>
+        <v>4.9093</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4158</v>
+        <v>4.6323</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8431999999999999</v>
+        <v>0.2769</v>
       </c>
       <c r="G2" t="n">
         <v>3.9478</v>
@@ -610,13 +610,13 @@
         <v>1.6676</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1085</v>
+        <v>-0.2413</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3319</v>
+        <v>0.5484</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2234</v>
+        <v>-0.7897</v>
       </c>
       <c r="V2" t="n">
         <v>1.5733</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. BENÍTEZ SIERRA</t>
+          <t>A. VEGUILLA SANCHEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6221</v>
+        <v>1.0505</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6221</v>
+        <v>0.654</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.3965</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6221</v>
+        <v>2.3501</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2.0462</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6221</v>
+        <v>0.3039</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6221</v>
+        <v>2.0853</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1.4513</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6221</v>
+        <v>0.634</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.2648</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.5949</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-0.3301</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.297</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-1.3552</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0.1899</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-1.1652</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0.315</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>-0.315</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. VEGUILLA SANCHEZ</t>
+          <t>F. BENÍTEZ SIERRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.609</v>
+        <v>0.6221</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3602</v>
+        <v>0.6221</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2488</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3501</v>
+        <v>0.6221</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0462</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3039</v>
+        <v>0.6221</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0853</v>
+        <v>0.6221</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4513</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.634</v>
+        <v>0.6221</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2648</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5949</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3301</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.297</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.7967</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4837</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.3129</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.315</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.315</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.353</v>
+        <v>0.5248</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2732</v>
+        <v>-0.1753</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6262</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>0.5438</v>
@@ -844,13 +844,13 @@
         <v>0.1853</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1908</v>
+        <v>-0.019</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1094</v>
+        <v>-0.0115</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0813</v>
+        <v>-0.0075</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.147</v>
+        <v>0.1716</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.147</v>
+        <v>0.1716</v>
       </c>
       <c r="G6" t="n">
         <v>0.2611</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1142</v>
+        <v>-0.0895</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1142</v>
+        <v>-0.0895</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. BRAVO ORTEGA</t>
+          <t>A. MARQUEZ MARQUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5081</v>
+        <v>-0.4633</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0336</v>
+        <v>1.1008</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4745</v>
+        <v>-1.5641</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4377</v>
+        <v>0.1781</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2611</v>
+        <v>2.2841</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6989</v>
+        <v>-2.106</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2.1819</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3.9118</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.7299</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4377</v>
+        <v>-2.0038</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2611</v>
+        <v>-1.6277</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6989</v>
+        <v>-0.3761</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.7411</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.594</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0704</v>
+        <v>-2.012</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0336</v>
+        <v>-0.1716</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0368</v>
+        <v>-1.8405</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.9433</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.3139</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. CORRALES GARCIA</t>
+          <t>M. BRAVO ORTEGA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8003</v>
+        <v>-0.582</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3146</v>
+        <v>-0.0336</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.115</v>
+        <v>-0.5484</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5626</v>
+        <v>-0.4377</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1386</v>
+        <v>0.2611</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.424</v>
+        <v>-0.6989</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3768</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1718</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5486</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1858</v>
+        <v>-0.4377</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3104</v>
+        <v>0.2611</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8754</v>
+        <v>-0.6989</v>
       </c>
       <c r="P8" t="n">
-        <v>1.297</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.297</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5347</v>
+        <v>-0.1443</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6914</v>
+        <v>-0.0336</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.2261</v>
+        <v>-0.1107</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8021</v>
+        <v>-0.7036</v>
       </c>
       <c r="E9" t="n">
         <v>-1.0282</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2261</v>
+        <v>0.3246</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2025</v>
@@ -1156,13 +1156,13 @@
         <v>0.7411</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4143</v>
+        <v>-0.3159</v>
       </c>
       <c r="T9" t="n">
         <v>0.3793</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7936</v>
+        <v>-0.6951000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. MARQUEZ MARQUEZ</t>
+          <t>C. CORRALES GARCIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1237</v>
+        <v>-0.8982</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3174</v>
+        <v>0.2167</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.441</v>
+        <v>-1.115</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1781</v>
+        <v>-1.5626</v>
       </c>
       <c r="H10" t="n">
-        <v>2.2841</v>
+        <v>-0.1386</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.106</v>
+        <v>-1.424</v>
       </c>
       <c r="J10" t="n">
-        <v>2.1819</v>
+        <v>-0.3768</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9118</v>
+        <v>0.1718</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.7299</v>
+        <v>-0.5486</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.0038</v>
+        <v>-1.1858</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6277</v>
+        <v>-0.3104</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3761</v>
+        <v>-0.8754</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7411</v>
+        <v>1.297</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.594</v>
+        <v>1.297</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.6724</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.955</v>
+        <v>0.5935</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.7174</v>
+        <v>-1.2261</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.9433</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3139</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2558</v>
+        <v>-3.4796</v>
       </c>
       <c r="E11" t="n">
-        <v>1.556</v>
+        <v>0.2829</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.8118</v>
+        <v>-3.7626</v>
       </c>
       <c r="G11" t="n">
         <v>-0.522</v>
@@ -1312,13 +1312,13 @@
         <v>2.2234</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3027</v>
+        <v>-0.9211</v>
       </c>
       <c r="T11" t="n">
-        <v>2.124</v>
+        <v>0.8509</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.8213</v>
+        <v>-1.7721</v>
       </c>
       <c r="V11" t="n">
         <v>-3.1482</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0604</v>
+        <v>-4.6189</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0472</v>
+        <v>-2.7534</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0132</v>
+        <v>-1.8655</v>
       </c>
       <c r="G12" t="n">
         <v>-1.7915</v>
@@ -1390,13 +1390,13 @@
         <v>0.9264</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8427</v>
+        <v>-1.4012</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5049</v>
+        <v>-0.2111</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.3378</v>
+        <v>-1.1901</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3144</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.8469</v>
+        <v>-6.284</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.7602</v>
+        <v>-2.1726</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.0868</v>
+        <v>-4.1114</v>
       </c>
       <c r="G13" t="n">
         <v>-1.253</v>
@@ -1468,13 +1468,13 @@
         <v>1.8529</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5199</v>
+        <v>-0.9569</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6267</v>
+        <v>-0.0391</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8931</v>
+        <v>-0.9177999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-3.1477</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.8538</v>
+        <v>-6.5097</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.6952</v>
+        <v>-4.5973</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.1586</v>
+        <v>-1.9123</v>
       </c>
       <c r="G14" t="n">
         <v>-4.0051</v>
@@ -1546,13 +1546,13 @@
         <v>1.1117</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6253</v>
+        <v>-1.2812</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0161</v>
+        <v>0.0818</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.6092</v>
+        <v>-1.3629</v>
       </c>
       <c r="V14" t="n">
         <v>0.6294</v>
@@ -1582,22 +1582,22 @@
         <v>-16.261</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.251500000000001</v>
+        <v>-3.251600000000001</v>
       </c>
       <c r="F15" t="n">
         <v>-13.0096</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.871400000000001</v>
+        <v>-1.8714</v>
       </c>
       <c r="H15" t="n">
-        <v>1.392700000000001</v>
+        <v>1.392699999999999</v>
       </c>
       <c r="I15" t="n">
         <v>-3.264399999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>7.260400000000002</v>
+        <v>7.260400000000004</v>
       </c>
       <c r="K15" t="n">
         <v>5.8027</v>
@@ -1627,10 +1627,10 @@
         <v>-9.370200000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7972</v>
+        <v>1.7971</v>
       </c>
       <c r="U15" t="n">
-        <v>-11.1671</v>
+        <v>-11.1672</v>
       </c>
       <c r="V15" t="n">
         <v>-4.0932</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>10.0642</v>
+        <v>12.4723</v>
       </c>
       <c r="E16" t="n">
-        <v>8.035500000000001</v>
+        <v>9.7982</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0287</v>
+        <v>2.6741</v>
       </c>
       <c r="G16" t="n">
         <v>5.5472</v>
@@ -1702,13 +1702,13 @@
         <v>2.594</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2972</v>
+        <v>2.1109</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1803</v>
+        <v>1.5824</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1169</v>
+        <v>0.5285</v>
       </c>
       <c r="V16" t="n">
         <v>3.1466</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>7.4172</v>
+        <v>7.483</v>
       </c>
       <c r="E17" t="n">
-        <v>5.2227</v>
+        <v>4.5372</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1944</v>
+        <v>2.9458</v>
       </c>
       <c r="G17" t="n">
         <v>4.0076</v>
@@ -1780,13 +1780,13 @@
         <v>1.8529</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4831</v>
+        <v>2.5489</v>
       </c>
       <c r="T17" t="n">
-        <v>2.7594</v>
+        <v>2.0739</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2763</v>
+        <v>0.475</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.9537</v>
+        <v>3.1712</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0268</v>
+        <v>1.7123</v>
       </c>
       <c r="F18" t="n">
-        <v>0.927</v>
+        <v>1.4589</v>
       </c>
       <c r="G18" t="n">
         <v>2.0065</v>
@@ -1858,13 +1858,13 @@
         <v>1.4823</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6277</v>
+        <v>0.5898</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1679</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4599</v>
+        <v>0.0721</v>
       </c>
       <c r="V18" t="n">
         <v>0.9455</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. PINILLA NUÑEZ</t>
+          <t>J. PINILLA NUNEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6441</v>
+        <v>1.5517</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6441</v>
+        <v>-0.2889</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1.8405</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6441</v>
+        <v>-3.475</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6441</v>
+        <v>-1.2541</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-2.221</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6441</v>
+        <v>-2.5278</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6441</v>
+        <v>-0.8595</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-1.6683</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-0.9472</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-0.3945</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-0.5527</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.8529</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.7793</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.5921</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.6379</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.9439</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.5733</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. GALLEGO CONTRERAS</t>
+          <t>J. RIBEIROS CARREIRAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6367</v>
+        <v>0.716</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6308</v>
+        <v>0.9051</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0059</v>
+        <v>-0.1891</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2671</v>
+        <v>-0.9127999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0539</v>
+        <v>0.8676</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3211</v>
+        <v>-1.7804</v>
       </c>
       <c r="J20" t="n">
-        <v>1.178</v>
+        <v>0.4266</v>
       </c>
       <c r="K20" t="n">
-        <v>1.095</v>
+        <v>1.7003</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0829</v>
+        <v>-1.2737</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9108000000000001</v>
+        <v>-1.3394</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.149</v>
+        <v>-0.8327</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2381</v>
+        <v>-0.5067</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.8529</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1102</v>
+        <v>0.6833</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3793</v>
+        <v>1.0726</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2691</v>
+        <v>-0.3892</v>
       </c>
       <c r="V20" t="n">
-        <v>0.63</v>
+        <v>0.9455</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X20" t="n">
-        <v>0.63</v>
+        <v>-0.3133</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. MOLINA LOPEZ</t>
+          <t>A. GALLEGO CONTRERAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4326</v>
+        <v>0.6854</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6042</v>
+        <v>0.7288</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1717</v>
+        <v>-0.0434</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5901999999999999</v>
+        <v>0.2671</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1985</v>
+        <v>-0.0539</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3917</v>
+        <v>0.3211</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2536</v>
+        <v>1.178</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3992</v>
+        <v>1.095</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6529</v>
+        <v>0.0829</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3366</v>
+        <v>-0.9108000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5977</v>
+        <v>-1.149</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2611</v>
+        <v>0.2381</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1853</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1853</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>0.523</v>
+        <v>0.1589</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5434</v>
+        <v>0.4772</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0204</v>
+        <v>-0.3184</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3144</v>
+        <v>0.63</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. PINILLA NUNEZ</t>
+          <t>J. PINILLA NUÑEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1887</v>
+        <v>0.6441</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9744</v>
+        <v>0.6441</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1631</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.475</v>
+        <v>0.6441</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2541</v>
+        <v>0.6441</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.221</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.5278</v>
+        <v>0.6441</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.8595</v>
+        <v>0.6441</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.6683</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9472</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3945</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5527</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.8529</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7793</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.867</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9066</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0396</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9439</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.5733</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. GARRIDO SOTO</t>
+          <t>M. MOLINA LOPEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,40 +2203,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1516</v>
+        <v>0.1875</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0409</v>
+        <v>0.4084</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1108</v>
+        <v>-0.2209</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1683</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2989</v>
+        <v>-0.1985</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1306</v>
+        <v>-0.3917</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.2536</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>0.3992</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-0.6529</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1683</v>
+        <v>-0.3366</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2989</v>
+        <v>-0.5977</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1306</v>
+        <v>0.2611</v>
       </c>
       <c r="P23" t="n">
         <v>0.1853</v>
@@ -2248,13 +2248,13 @@
         <v>0.1853</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1798</v>
+        <v>0.2779</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2736</v>
+        <v>0.3476</v>
       </c>
       <c r="U23" t="n">
-        <v>0.09379999999999999</v>
+        <v>-0.0696</v>
       </c>
       <c r="V23" t="n">
         <v>0.3144</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. MALPICA PEREZ</t>
+          <t>F. GARRIDO SOTO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.101</v>
+        <v>0.1757</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0332</v>
+        <v>0.1388</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0677</v>
+        <v>0.0369</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0679</v>
+        <v>-0.1683</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-0.2989</v>
       </c>
       <c r="I24" t="n">
         <v>0.1306</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0215</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0215</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0464</v>
+        <v>-0.1683</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.2989</v>
       </c>
       <c r="O24" t="n">
         <v>0.1306</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1689</v>
+        <v>-0.1558</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0547</v>
+        <v>-0.1756</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1142</v>
+        <v>0.0199</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. RIBEIROS CARREIRAS</t>
+          <t>J. MALPICA PEREZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.746</v>
+        <v>0.1522</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0742</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6718</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.9127999999999999</v>
+        <v>0.0679</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8676</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.7804</v>
+        <v>0.1306</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4266</v>
+        <v>0.0215</v>
       </c>
       <c r="K25" t="n">
-        <v>1.7003</v>
+        <v>0.0215</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.2737</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.3394</v>
+        <v>0.0464</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.8327</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.5067</v>
+        <v>0.1306</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8529</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7786999999999999</v>
+        <v>0.0843</v>
       </c>
       <c r="T25" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.0432</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.872</v>
+        <v>0.041</v>
       </c>
       <c r="V25" t="n">
-        <v>0.9455</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.3133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.0969</v>
+        <v>-0.9422</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.9382</v>
+        <v>-0.8403</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1587</v>
+        <v>-0.102</v>
       </c>
       <c r="G26" t="n">
         <v>-0.0789</v>
@@ -2482,13 +2482,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.0915</v>
+        <v>0.0631</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.0547</v>
+        <v>0.0432</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0368</v>
+        <v>0.0199</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.6052</v>
+        <v>-2.8157</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.3335</v>
+        <v>-3.7045</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7282999999999999</v>
+        <v>0.8888</v>
       </c>
       <c r="G27" t="n">
         <v>-3.5165</v>
@@ -2560,13 +2560,13 @@
         <v>1.6676</v>
       </c>
       <c r="S27" t="n">
-        <v>3.9669</v>
+        <v>2.7563</v>
       </c>
       <c r="T27" t="n">
-        <v>3.2817</v>
+        <v>1.9107</v>
       </c>
       <c r="U27" t="n">
-        <v>0.6852</v>
+        <v>0.8456</v>
       </c>
       <c r="V27" t="n">
         <v>-0.9439</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.6788</v>
+        <v>-3.9558</v>
       </c>
       <c r="E28" t="n">
-        <v>1.1579</v>
+        <v>-1.0945</v>
       </c>
       <c r="F28" t="n">
-        <v>-2.8366</v>
+        <v>-2.8613</v>
       </c>
       <c r="G28" t="n">
         <v>-1.9275</v>
@@ -2638,13 +2638,13 @@
         <v>1.6676</v>
       </c>
       <c r="S28" t="n">
-        <v>3.5637</v>
+        <v>1.2868</v>
       </c>
       <c r="T28" t="n">
-        <v>3.9346</v>
+        <v>1.6822</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.3708</v>
+        <v>-0.3955</v>
       </c>
       <c r="V28" t="n">
         <v>-2.2033</v>
@@ -2671,16 +2671,16 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>16.2609</v>
+        <v>19.5254</v>
       </c>
       <c r="E29" t="n">
         <v>13.0094</v>
       </c>
       <c r="F29" t="n">
-        <v>3.2517</v>
+        <v>6.515799999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>1.871200000000001</v>
+        <v>1.871199999999999</v>
       </c>
       <c r="H29" t="n">
         <v>-1.3931</v>
@@ -2689,13 +2689,13 @@
         <v>3.2643</v>
       </c>
       <c r="J29" t="n">
-        <v>9.131799999999997</v>
+        <v>9.131799999999998</v>
       </c>
       <c r="K29" t="n">
         <v>4.409699999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>4.7219</v>
+        <v>4.721899999999999</v>
       </c>
       <c r="M29" t="n">
         <v>-7.2605</v>
@@ -2716,13 +2716,13 @@
         <v>14.8231</v>
       </c>
       <c r="S29" t="n">
-        <v>9.370100000000001</v>
+        <v>12.6344</v>
       </c>
       <c r="T29" t="n">
         <v>11.1671</v>
       </c>
       <c r="U29" t="n">
-        <v>-1.797</v>
+        <v>1.4672</v>
       </c>
       <c r="V29" t="n">
         <v>4.0931</v>
